--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>136040040</v>
       </c>
       <c r="B107" t="n">
-        <v>56893</v>
+        <v>56894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>136040298</v>
       </c>
       <c r="B110" t="n">
-        <v>56907</v>
+        <v>56908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>136040578</v>
       </c>
       <c r="B140" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>136040113</v>
       </c>
       <c r="B142" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>136039907</v>
       </c>
       <c r="B143" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -13165,7 +13165,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Helena  Andresson Tsiamanis</t>
+          <t>Via Helena  Andresson Tsiamanis</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -9383,7 +9383,7 @@
         <v>137137505</v>
       </c>
       <c r="B76" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>137137696</v>
       </c>
       <c r="B81" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>136040040</v>
       </c>
       <c r="B107" t="n">
-        <v>56894</v>
+        <v>56897</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>136040298</v>
       </c>
       <c r="B110" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>136040578</v>
       </c>
       <c r="B140" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>136040113</v>
       </c>
       <c r="B142" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>136039907</v>
       </c>
       <c r="B143" t="n">
-        <v>56915</v>
+        <v>56918</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
